--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.86151</v>
+        <v>17.01088</v>
       </c>
       <c r="D2" t="n">
         <v>16.54456</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01088</v>
+        <v>16.86151</v>
       </c>
       <c r="F2" t="n">
         <v>42.29472</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.86531</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.65944</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.665</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.86531</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.65944</v>
       </c>
       <c r="F4" t="n">
         <v>41.92764</v>
